--- a/04_Features/modules/c_data/module_contrasts.xlsx
+++ b/04_Features/modules/c_data/module_contrasts.xlsx
@@ -459,16 +459,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.17425092658077</v>
+        <v>0.163440551488145</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3274237199715</v>
+        <v>2.18610964342696</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0204071679468525</v>
+        <v>0.029347354796083</v>
       </c>
       <c r="F2" t="n">
-        <v>0.224478847415378</v>
+        <v>0.236962350301216</v>
       </c>
     </row>
     <row r="3">
@@ -479,16 +479,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00461843191688611</v>
+        <v>0.00984263494844101</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0616871783889867</v>
+        <v>0.131650798908855</v>
       </c>
       <c r="E3" t="n">
-        <v>0.950840679229933</v>
+        <v>0.895322222176802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960146595097477</v>
+        <v>0.895322222176802</v>
       </c>
     </row>
     <row r="4">
@@ -499,16 +499,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.145404468260077</v>
+        <v>0.015351710135656</v>
       </c>
       <c r="D4" t="n">
-        <v>1.94212917577503</v>
+        <v>0.205337789582088</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0527756256599646</v>
+        <v>0.837405617197178</v>
       </c>
       <c r="F4" t="n">
-        <v>0.255336764787751</v>
+        <v>0.895322222176802</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.119870424819134</v>
+        <v>-0.127629100798965</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.60107768447242</v>
+        <v>-1.70711127378182</v>
       </c>
       <c r="E5" t="n">
-        <v>0.110095794873296</v>
+        <v>0.0885249459641226</v>
       </c>
       <c r="F5" t="n">
-        <v>0.255336764787751</v>
+        <v>0.265231963101765</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +539,16 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0695662929791277</v>
+        <v>0.0100615119654476</v>
       </c>
       <c r="D6" t="n">
-        <v>0.929178648097797</v>
+        <v>0.1345784025742</v>
       </c>
       <c r="E6" t="n">
-        <v>0.35331903045467</v>
+        <v>0.893008333416084</v>
       </c>
       <c r="F6" t="n">
-        <v>0.485813666875172</v>
+        <v>0.895322222176802</v>
       </c>
     </row>
     <row r="7">
@@ -559,16 +559,16 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.102069989661726</v>
+        <v>-0.102025442833883</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3633219615956</v>
+        <v>-1.36464789443785</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17349609883131</v>
+        <v>0.173079085736162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.318076181190734</v>
+        <v>0.317311657182965</v>
       </c>
     </row>
     <row r="8">
@@ -579,16 +579,16 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0182622226962919</v>
+        <v>0.124553760281588</v>
       </c>
       <c r="D8" t="n">
-        <v>0.243923697375864</v>
+        <v>1.66597685823656</v>
       </c>
       <c r="E8" t="n">
-        <v>0.807406522566315</v>
+        <v>0.09644798658246</v>
       </c>
       <c r="F8" t="n">
-        <v>0.960146595097477</v>
+        <v>0.265231963101765</v>
       </c>
     </row>
     <row r="9">
@@ -599,16 +599,16 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>0.125170010431124</v>
+        <v>0.0697153223915064</v>
       </c>
       <c r="D9" t="n">
-        <v>1.67186285331712</v>
+        <v>0.932481793453485</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0952805350550737</v>
+        <v>0.351612083078058</v>
       </c>
       <c r="F9" t="n">
-        <v>0.255336764787751</v>
+        <v>0.48346661423233</v>
       </c>
     </row>
     <row r="10">
@@ -619,16 +619,16 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0872939501086421</v>
+        <v>0.079943899575923</v>
       </c>
       <c r="D10" t="n">
-        <v>1.16596229402939</v>
+        <v>1.06929478764491</v>
       </c>
       <c r="E10" t="n">
-        <v>0.244277496561677</v>
+        <v>0.285538134588101</v>
       </c>
       <c r="F10" t="n">
-        <v>0.383864637454063</v>
+        <v>0.448702782924159</v>
       </c>
     </row>
     <row r="11">
@@ -639,16 +639,16 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.117895785723807</v>
+        <v>-0.115888431052053</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.57470295029437</v>
+        <v>-1.55007318794376</v>
       </c>
       <c r="E11" t="n">
-        <v>0.116062165812614</v>
+        <v>0.121861319342874</v>
       </c>
       <c r="F11" t="n">
-        <v>0.255336764787751</v>
+        <v>0.268094902554322</v>
       </c>
     </row>
     <row r="12">
@@ -659,16 +659,16 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0037433413698872</v>
+        <v>0.151688130833931</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0499988244951321</v>
+        <v>2.02891438256998</v>
       </c>
       <c r="E12" t="n">
-        <v>0.960146595097477</v>
+        <v>0.0430840636911303</v>
       </c>
       <c r="F12" t="n">
-        <v>0.960146595097477</v>
+        <v>0.236962350301216</v>
       </c>
     </row>
     <row r="13">
@@ -679,16 +679,16 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0887187279761334</v>
+        <v>0.0599806462511723</v>
       </c>
       <c r="D13" t="n">
-        <v>1.27700058066186</v>
+        <v>0.865771988156715</v>
       </c>
       <c r="E13" t="n">
-        <v>0.202292779264323</v>
+        <v>0.387099121710436</v>
       </c>
       <c r="F13" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="14">
@@ -699,16 +699,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00664479106411173</v>
+        <v>0.0324948861199908</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0956438650645454</v>
+        <v>0.469037329861724</v>
       </c>
       <c r="E14" t="n">
-        <v>0.923848085773366</v>
+        <v>0.639281220645106</v>
       </c>
       <c r="F14" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="15">
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0113712482267952</v>
+        <v>0.00640984062376629</v>
       </c>
       <c r="D15" t="n">
-        <v>0.163675594992457</v>
+        <v>0.0925208514320959</v>
       </c>
       <c r="E15" t="n">
-        <v>0.870063610774027</v>
+        <v>0.926327414679895</v>
       </c>
       <c r="F15" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="16">
@@ -739,16 +739,16 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.00433049874317533</v>
+        <v>-0.0201423238526641</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0623323793717828</v>
+        <v>-0.290738110673101</v>
       </c>
       <c r="E16" t="n">
-        <v>0.950327173765851</v>
+        <v>0.771392121562186</v>
       </c>
       <c r="F16" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="17">
@@ -759,16 +759,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0154778749012223</v>
+        <v>0.017186749613667</v>
       </c>
       <c r="D17" t="n">
-        <v>0.222785602173982</v>
+        <v>0.248076793315399</v>
       </c>
       <c r="E17" t="n">
-        <v>0.823808406517541</v>
+        <v>0.804193690430241</v>
       </c>
       <c r="F17" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="18">
@@ -779,16 +779,16 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.00666295405271881</v>
+        <v>-0.00701978614699099</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0959052996852496</v>
+        <v>-0.101324920432923</v>
       </c>
       <c r="E18" t="n">
-        <v>0.92364056880673</v>
+        <v>0.919339873221008</v>
       </c>
       <c r="F18" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="19">
@@ -799,16 +799,16 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0133069405380289</v>
+        <v>0.020024990292107</v>
       </c>
       <c r="D19" t="n">
-        <v>0.191537583794789</v>
+        <v>0.289044495876493</v>
       </c>
       <c r="E19" t="n">
-        <v>0.848195058698829</v>
+        <v>0.772686950588943</v>
       </c>
       <c r="F19" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="20">
@@ -819,16 +819,16 @@
         <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>0.023496990295322</v>
+        <v>0.0115077229662646</v>
       </c>
       <c r="D20" t="n">
-        <v>0.338211231556479</v>
+        <v>0.166104648988587</v>
       </c>
       <c r="E20" t="n">
-        <v>0.735369463411301</v>
+        <v>0.86815284917739</v>
       </c>
       <c r="F20" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="21">
@@ -839,16 +839,16 @@
         <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00479271567000719</v>
+        <v>0.00560771240019357</v>
       </c>
       <c r="D21" t="n">
-        <v>0.068985442343051</v>
+        <v>0.0809427809996588</v>
       </c>
       <c r="E21" t="n">
-        <v>0.94503334984807</v>
+        <v>0.935525204626051</v>
       </c>
       <c r="F21" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="22">
@@ -859,16 +859,16 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0207367056611498</v>
+        <v>-0.0200855892274226</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.298480216910076</v>
+        <v>-0.289919192365902</v>
       </c>
       <c r="E22" t="n">
-        <v>0.765481190564536</v>
+        <v>0.772018134318984</v>
       </c>
       <c r="F22" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="23">
@@ -879,16 +879,16 @@
         <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0177842856521897</v>
+        <v>0.0199833944208887</v>
       </c>
       <c r="D23" t="n">
-        <v>0.25598364204018</v>
+        <v>0.288444093207056</v>
       </c>
       <c r="E23" t="n">
-        <v>0.798086166305484</v>
+        <v>0.773146132606368</v>
       </c>
       <c r="F23" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
     <row r="24">
@@ -899,16 +899,16 @@
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.134267572014771</v>
+        <v>-0.122966682906332</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.80780236586594</v>
+        <v>-1.6602897009255</v>
       </c>
       <c r="E24" t="n">
-        <v>0.071337504857376</v>
+        <v>0.0975868817644897</v>
       </c>
       <c r="F24" t="n">
-        <v>0.156942510686227</v>
+        <v>0.214691139881877</v>
       </c>
     </row>
     <row r="25">
@@ -919,16 +919,16 @@
         <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>0.138659313379964</v>
+        <v>0.136019740501266</v>
       </c>
       <c r="D25" t="n">
-        <v>1.8669335493016</v>
+        <v>1.83653139971935</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0625927404040017</v>
+        <v>0.0669708208120773</v>
       </c>
       <c r="F25" t="n">
-        <v>0.156942510686227</v>
+        <v>0.184169757233212</v>
       </c>
     </row>
     <row r="26">
@@ -939,16 +939,16 @@
         <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.201537382986135</v>
+        <v>-0.184370431711183</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.71353501300137</v>
+        <v>-2.48935989562669</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00692506393730139</v>
+        <v>0.0131752591918906</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0761757033103153</v>
+        <v>0.0697935914744919</v>
       </c>
     </row>
     <row r="27">
@@ -959,16 +959,16 @@
         <v>10</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0860009796394341</v>
+        <v>0.076664332400634</v>
       </c>
       <c r="D27" t="n">
-        <v>1.15793241901963</v>
+        <v>1.03511779373653</v>
       </c>
       <c r="E27" t="n">
-        <v>0.24753585628794</v>
+        <v>0.301197033966177</v>
       </c>
       <c r="F27" t="n">
-        <v>0.45381573652789</v>
+        <v>0.473309624803992</v>
       </c>
     </row>
     <row r="28">
@@ -979,16 +979,16 @@
         <v>11</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0756058703989498</v>
+        <v>0.174327763077681</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.01797082742762</v>
+        <v>2.35376431064444</v>
       </c>
       <c r="E28" t="n">
-        <v>0.309265558677127</v>
+        <v>0.0190346158566796</v>
       </c>
       <c r="F28" t="n">
-        <v>0.485988735064057</v>
+        <v>0.0697935914744919</v>
       </c>
     </row>
     <row r="29">
@@ -999,16 +999,16 @@
         <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0580905756380288</v>
+        <v>0.0609189079196564</v>
       </c>
       <c r="D29" t="n">
-        <v>0.782141797137653</v>
+        <v>0.822523898507362</v>
       </c>
       <c r="E29" t="n">
-        <v>0.434562721128356</v>
+        <v>0.411235730263329</v>
       </c>
       <c r="F29" t="n">
-        <v>0.531132214712436</v>
+        <v>0.502621448099624</v>
       </c>
     </row>
     <row r="30">
@@ -1019,16 +1019,16 @@
         <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>0.172240437979974</v>
+        <v>-0.00630213084190683</v>
       </c>
       <c r="D30" t="n">
-        <v>2.31907575750104</v>
+        <v>-0.0850910399744067</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0208598776799607</v>
+        <v>0.932228708918963</v>
       </c>
       <c r="F30" t="n">
-        <v>0.076486218159856</v>
+        <v>0.932228708918963</v>
       </c>
     </row>
     <row r="31">
@@ -1039,16 +1039,16 @@
         <v>14</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.012242707258276</v>
+        <v>-0.0801913374957558</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.164837978478382</v>
+        <v>-1.08273923147998</v>
       </c>
       <c r="E31" t="n">
-        <v>0.869149151821834</v>
+        <v>0.279532375115614</v>
       </c>
       <c r="F31" t="n">
-        <v>0.869149151821834</v>
+        <v>0.473309624803992</v>
       </c>
     </row>
     <row r="32">
@@ -1059,16 +1059,16 @@
         <v>15</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.032247605111012</v>
+        <v>-0.013865770340698</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.434187465658383</v>
+        <v>-0.187214903646668</v>
       </c>
       <c r="E32" t="n">
-        <v>0.664370598154253</v>
+        <v>0.85158064816306</v>
       </c>
       <c r="F32" t="n">
-        <v>0.730807657969679</v>
+        <v>0.932228708918963</v>
       </c>
     </row>
     <row r="33">
@@ -1079,16 +1079,16 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0663536601440665</v>
+        <v>0.0634319103425053</v>
       </c>
       <c r="D33" t="n">
-        <v>0.893397430163637</v>
+        <v>0.85645432537132</v>
       </c>
       <c r="E33" t="n">
-        <v>0.372145270872292</v>
+        <v>0.392224659362268</v>
       </c>
       <c r="F33" t="n">
-        <v>0.511699747449401</v>
+        <v>0.502621448099624</v>
       </c>
     </row>
     <row r="34">
@@ -1099,16 +1099,16 @@
         <v>17</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.182328952689138</v>
+        <v>-0.188846736971503</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.45490930603124</v>
+        <v>-2.54979873439385</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0144880606336468</v>
+        <v>0.0111252882346163</v>
       </c>
       <c r="F34" t="n">
-        <v>0.076486218159856</v>
+        <v>0.0697935914744919</v>
       </c>
     </row>
     <row r="35">
@@ -1119,16 +1119,16 @@
         <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0229610877851472</v>
+        <v>-0.0022894138023219</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.330497552243409</v>
+        <v>-0.033045831667926</v>
       </c>
       <c r="E35" t="n">
-        <v>0.741185386719181</v>
+        <v>0.973653408327096</v>
       </c>
       <c r="F35" t="n">
-        <v>0.815303925391099</v>
+        <v>0.973653408327096</v>
       </c>
     </row>
     <row r="36">
@@ -1139,16 +1139,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="n">
-        <v>0.171674155243678</v>
+        <v>0.0923161271859973</v>
       </c>
       <c r="D36" t="n">
-        <v>2.47104530161644</v>
+        <v>1.33250843343801</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0138594053081593</v>
+        <v>0.183400504194503</v>
       </c>
       <c r="F36" t="n">
-        <v>0.152453458389753</v>
+        <v>0.615570301973216</v>
       </c>
     </row>
     <row r="37">
@@ -1159,16 +1159,16 @@
         <v>9</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00616101253664516</v>
+        <v>-0.100111689545185</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0886804484942274</v>
+        <v>-1.44503105438895</v>
       </c>
       <c r="E37" t="n">
-        <v>0.929377253711649</v>
+        <v>0.149179187303412</v>
       </c>
       <c r="F37" t="n">
-        <v>0.929377253711649</v>
+        <v>0.615570301973216</v>
       </c>
     </row>
     <row r="38">
@@ -1179,16 +1179,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0877014718973078</v>
+        <v>-0.0749696021627394</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.26235838917675</v>
+        <v>-1.08212541165283</v>
       </c>
       <c r="E38" t="n">
-        <v>0.207505651047244</v>
+        <v>0.279804682715098</v>
       </c>
       <c r="F38" t="n">
-        <v>0.540898714652634</v>
+        <v>0.615570301973216</v>
       </c>
     </row>
     <row r="39">
@@ -1199,16 +1199,16 @@
         <v>11</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.0435137770911641</v>
+        <v>0.0386932087352775</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.626329072562398</v>
+        <v>0.558505090369032</v>
       </c>
       <c r="E39" t="n">
-        <v>0.531432234719305</v>
+        <v>0.576790909497371</v>
       </c>
       <c r="F39" t="n">
-        <v>0.751880675854233</v>
+        <v>0.728755774886901</v>
       </c>
     </row>
     <row r="40">
@@ -1219,16 +1219,16 @@
         <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0390834897963618</v>
+        <v>0.0411641619392544</v>
       </c>
       <c r="D40" t="n">
-        <v>0.562560355663264</v>
+        <v>0.594171296082971</v>
       </c>
       <c r="E40" t="n">
-        <v>0.574028137538539</v>
+        <v>0.552710741564234</v>
       </c>
       <c r="F40" t="n">
-        <v>0.751880675854233</v>
+        <v>0.728755774886901</v>
       </c>
     </row>
     <row r="41">
@@ -1239,16 +1239,16 @@
         <v>13</v>
       </c>
       <c r="C41" t="n">
-        <v>0.034950254340995</v>
+        <v>0.083296048864987</v>
       </c>
       <c r="D41" t="n">
-        <v>0.503067346724548</v>
+        <v>1.20231091758251</v>
       </c>
       <c r="E41" t="n">
-        <v>0.615175098426191</v>
+        <v>0.229906291317126</v>
       </c>
       <c r="F41" t="n">
-        <v>0.751880675854233</v>
+        <v>0.615570301973216</v>
       </c>
     </row>
     <row r="42">
@@ -1259,16 +1259,16 @@
         <v>14</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0807323044692387</v>
+        <v>-0.0367315190075245</v>
       </c>
       <c r="D42" t="n">
-        <v>1.16204551211692</v>
+        <v>-0.530189689954184</v>
       </c>
       <c r="E42" t="n">
-        <v>0.245863052114834</v>
+        <v>0.596254724907464</v>
       </c>
       <c r="F42" t="n">
-        <v>0.540898714652634</v>
+        <v>0.728755774886901</v>
       </c>
     </row>
     <row r="43">
@@ -1279,16 +1279,16 @@
         <v>15</v>
       </c>
       <c r="C43" t="n">
-        <v>0.086693100125935</v>
+        <v>0.105570069561678</v>
       </c>
       <c r="D43" t="n">
-        <v>1.24784407673178</v>
+        <v>1.52381834352894</v>
       </c>
       <c r="E43" t="n">
-        <v>0.212768837336716</v>
+        <v>0.128290895611022</v>
       </c>
       <c r="F43" t="n">
-        <v>0.540898714652634</v>
+        <v>0.615570301973216</v>
       </c>
     </row>
     <row r="44">
@@ -1299,16 +1299,16 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0521917982384489</v>
+        <v>-0.0528908827597301</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.751238866659759</v>
+        <v>-0.763437001503801</v>
       </c>
       <c r="E44" t="n">
-        <v>0.452920807250981</v>
+        <v>0.445622448787831</v>
       </c>
       <c r="F44" t="n">
-        <v>0.751880675854233</v>
+        <v>0.728755774886901</v>
       </c>
     </row>
     <row r="45">
@@ -1319,16 +1319,16 @@
         <v>17</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.109832299275072</v>
+        <v>0.0170929005462158</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.58090533024126</v>
+        <v>0.246722158132349</v>
       </c>
       <c r="E45" t="n">
-        <v>0.114636651070569</v>
+        <v>0.80524127343169</v>
       </c>
       <c r="F45" t="n">
-        <v>0.540898714652634</v>
+        <v>0.885765400774859</v>
       </c>
     </row>
     <row r="46">
@@ -1339,16 +1339,16 @@
         <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0824913161283707</v>
+        <v>-0.0892040134700857</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.07908274152652</v>
+        <v>-1.1564569324821</v>
       </c>
       <c r="E46" t="n">
-        <v>0.281157166697679</v>
+        <v>0.248137884170261</v>
       </c>
       <c r="F46" t="n">
-        <v>0.817821017702153</v>
+        <v>0.787998430293093</v>
       </c>
     </row>
     <row r="47">
@@ -1359,16 +1359,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0380302779130285</v>
+        <v>0.0523538404814075</v>
       </c>
       <c r="D47" t="n">
-        <v>0.49748044372991</v>
+        <v>0.678724638181096</v>
       </c>
       <c r="E47" t="n">
-        <v>0.619105171121224</v>
+        <v>0.497678323411785</v>
       </c>
       <c r="F47" t="n">
-        <v>0.817821017702153</v>
+        <v>0.787998430293093</v>
       </c>
     </row>
     <row r="48">
@@ -1379,16 +1379,16 @@
         <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0479359899891019</v>
+        <v>-0.0521669247807174</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.62705872475997</v>
+        <v>-0.676301429297952</v>
       </c>
       <c r="E48" t="n">
-        <v>0.530954309851595</v>
+        <v>0.499213728810329</v>
       </c>
       <c r="F48" t="n">
-        <v>0.817821017702153</v>
+        <v>0.787998430293093</v>
       </c>
     </row>
     <row r="49">
@@ -1399,16 +1399,16 @@
         <v>10</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0664936558031391</v>
+        <v>0.0597525285068298</v>
       </c>
       <c r="D49" t="n">
-        <v>0.869814663721854</v>
+        <v>0.77464256524994</v>
       </c>
       <c r="E49" t="n">
-        <v>0.384888103779534</v>
+        <v>0.438977626701592</v>
       </c>
       <c r="F49" t="n">
-        <v>0.817821017702153</v>
+        <v>0.787998430293093</v>
       </c>
     </row>
     <row r="50">
@@ -1419,16 +1419,16 @@
         <v>11</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.101254381201523</v>
+        <v>0.000790828480422799</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.32452554264597</v>
+        <v>0.0102524431694536</v>
       </c>
       <c r="E50" t="n">
-        <v>0.186033723986584</v>
+        <v>0.991824643102634</v>
       </c>
       <c r="F50" t="n">
-        <v>0.817821017702153</v>
+        <v>0.991824643102634</v>
       </c>
     </row>
     <row r="51">
@@ -1439,16 +1439,16 @@
         <v>12</v>
       </c>
       <c r="C51" t="n">
-        <v>0.055700183525113</v>
+        <v>0.0563406617206116</v>
       </c>
       <c r="D51" t="n">
-        <v>0.728623442596978</v>
+        <v>0.730410508371124</v>
       </c>
       <c r="E51" t="n">
-        <v>0.466629583619688</v>
+        <v>0.465537979376877</v>
       </c>
       <c r="F51" t="n">
-        <v>0.817821017702153</v>
+        <v>0.787998430293093</v>
       </c>
     </row>
     <row r="52">
@@ -1459,16 +1459,16 @@
         <v>13</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0205292519744194</v>
+        <v>-0.0254205461990204</v>
       </c>
       <c r="D52" t="n">
-        <v>0.268546588195678</v>
+        <v>-0.329556549484144</v>
       </c>
       <c r="E52" t="n">
-        <v>0.788407708561996</v>
+        <v>0.741895903803947</v>
       </c>
       <c r="F52" t="n">
-        <v>0.817821017702153</v>
+        <v>0.906761660204824</v>
       </c>
     </row>
     <row r="53">
@@ -1479,16 +1479,16 @@
         <v>14</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0248568094299941</v>
+        <v>-0.0954773365369553</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.325156093079903</v>
+        <v>-1.23778542509318</v>
       </c>
       <c r="E53" t="n">
-        <v>0.745221450791998</v>
+        <v>0.216472628996663</v>
       </c>
       <c r="F53" t="n">
-        <v>0.817821017702153</v>
+        <v>0.787998430293093</v>
       </c>
     </row>
     <row r="54">
@@ -1499,16 +1499,16 @@
         <v>15</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0176199755287301</v>
+        <v>-0.00592999795042485</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.230489855072551</v>
+        <v>-0.0768775638292684</v>
       </c>
       <c r="E54" t="n">
-        <v>0.817821017702153</v>
+        <v>0.93875678641436</v>
       </c>
       <c r="F54" t="n">
-        <v>0.817821017702153</v>
+        <v>0.991824643102634</v>
       </c>
     </row>
     <row r="55">
@@ -1519,16 +1519,16 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0327548964787683</v>
+        <v>0.0303885736072217</v>
       </c>
       <c r="D55" t="n">
-        <v>0.428472294413673</v>
+        <v>0.393962953562611</v>
       </c>
       <c r="E55" t="n">
-        <v>0.668522347161275</v>
+        <v>0.693804135936233</v>
       </c>
       <c r="F55" t="n">
-        <v>0.817821017702153</v>
+        <v>0.906761660204824</v>
       </c>
     </row>
     <row r="56">
@@ -1539,16 +1539,16 @@
         <v>17</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0398879738502371</v>
+        <v>-0.0518948045893386</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.521781275852969</v>
+        <v>-0.672773614017601</v>
       </c>
       <c r="E56" t="n">
-        <v>0.602091909135782</v>
+        <v>0.50145354655015</v>
       </c>
       <c r="F56" t="n">
-        <v>0.817821017702153</v>
+        <v>0.787998430293093</v>
       </c>
     </row>
     <row r="57">
@@ -1559,16 +1559,16 @@
         <v>7</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00304088247626602</v>
+        <v>0.0142558917668867</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0397643254502858</v>
+        <v>0.184729178423445</v>
       </c>
       <c r="E57" t="n">
-        <v>0.968299516204039</v>
+        <v>0.853528754311322</v>
       </c>
       <c r="F57" t="n">
-        <v>0.968299516204039</v>
+        <v>0.934619895185784</v>
       </c>
     </row>
     <row r="58">
@@ -1579,16 +1579,16 @@
         <v>8</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0360039187658029</v>
+        <v>0.0297015893098577</v>
       </c>
       <c r="D58" t="n">
-        <v>0.470807916604204</v>
+        <v>0.384875971338749</v>
       </c>
       <c r="E58" t="n">
-        <v>0.638017204278547</v>
+        <v>0.700520042093063</v>
       </c>
       <c r="F58" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="59">
@@ -1599,16 +1599,16 @@
         <v>9</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0860972300441796</v>
+        <v>-0.0432250552688277</v>
       </c>
       <c r="D59" t="n">
-        <v>1.12585682036907</v>
+        <v>-0.560114307662309</v>
       </c>
       <c r="E59" t="n">
-        <v>0.260855560091162</v>
+        <v>0.575693828960525</v>
       </c>
       <c r="F59" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="60">
@@ -1619,16 +1619,16 @@
         <v>10</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0490462702728194</v>
+        <v>-0.0477342484394711</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.641357194325341</v>
+        <v>-0.618544854371451</v>
       </c>
       <c r="E60" t="n">
-        <v>0.521633130972589</v>
+        <v>0.536544511799657</v>
       </c>
       <c r="F60" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="61">
@@ -1639,16 +1639,16 @@
         <v>11</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0471659631236178</v>
+        <v>-0.00633440916779664</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.616769218298341</v>
+        <v>-0.0820818662556778</v>
       </c>
       <c r="E61" t="n">
-        <v>0.53771412692509</v>
+        <v>0.934619895185784</v>
       </c>
       <c r="F61" t="n">
-        <v>0.779798805229336</v>
+        <v>0.934619895185784</v>
       </c>
     </row>
     <row r="62">
@@ -1659,16 +1659,16 @@
         <v>12</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0397068520838941</v>
+        <v>-0.0386649949662801</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.519229599037026</v>
+        <v>-0.501024619901937</v>
       </c>
       <c r="E62" t="n">
-        <v>0.603868400994964</v>
+        <v>0.616610765504908</v>
       </c>
       <c r="F62" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="63">
@@ -1679,16 +1679,16 @@
         <v>13</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0254845341326823</v>
+        <v>0.0791082237904604</v>
       </c>
       <c r="D63" t="n">
-        <v>0.333250402509882</v>
+        <v>1.0250917603972</v>
       </c>
       <c r="E63" t="n">
-        <v>0.739108082512013</v>
+        <v>0.305897554077598</v>
       </c>
       <c r="F63" t="n">
-        <v>0.813018890763214</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="64">
@@ -1699,16 +1699,16 @@
         <v>14</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0768162107058077</v>
+        <v>-0.0372697371117135</v>
       </c>
       <c r="D64" t="n">
-        <v>1.00449288198544</v>
+        <v>-0.482944738167591</v>
       </c>
       <c r="E64" t="n">
-        <v>0.315707331909155</v>
+        <v>0.629381331979864</v>
       </c>
       <c r="F64" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="65">
@@ -1719,16 +1719,16 @@
         <v>15</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0648812589099049</v>
+        <v>0.0684061892253046</v>
       </c>
       <c r="D65" t="n">
-        <v>0.848424598797949</v>
+        <v>0.886413795875003</v>
       </c>
       <c r="E65" t="n">
-        <v>0.39667468693565</v>
+        <v>0.375891207982067</v>
       </c>
       <c r="F65" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="66">
@@ -1739,16 +1739,16 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.064404183583889</v>
+        <v>-0.065414268217409</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.842186087880128</v>
+        <v>-0.847644203713804</v>
       </c>
       <c r="E66" t="n">
-        <v>0.400153048945474</v>
+        <v>0.397108801556765</v>
       </c>
       <c r="F66" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="67">
@@ -1759,16 +1759,16 @@
         <v>17</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0539289181325395</v>
+        <v>0.0798099318237034</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.70520550154156</v>
+        <v>1.03418455870079</v>
       </c>
       <c r="E67" t="n">
-        <v>0.481065066356249</v>
+        <v>0.301632515348916</v>
       </c>
       <c r="F67" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="68">
@@ -1779,16 +1779,16 @@
         <v>7</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.108265601753358</v>
+        <v>-0.106421377337123</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.41574317876234</v>
+        <v>-1.3790181578007</v>
       </c>
       <c r="E68" t="n">
-        <v>0.157576284908472</v>
+        <v>0.168607688667761</v>
       </c>
       <c r="F68" t="n">
-        <v>0.346667826798639</v>
+        <v>0.393587088958638</v>
       </c>
     </row>
     <row r="69">
@@ -1799,16 +1799,16 @@
         <v>8</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00298907690208906</v>
+        <v>0.0734052026251266</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0390868860136125</v>
+        <v>0.951191478911423</v>
       </c>
       <c r="E69" t="n">
-        <v>0.968839299111306</v>
+        <v>0.34204275839881</v>
       </c>
       <c r="F69" t="n">
-        <v>0.968839299111306</v>
+        <v>0.537495763198129</v>
       </c>
     </row>
     <row r="70">
@@ -1819,16 +1819,16 @@
         <v>9</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.121601165478601</v>
+        <v>-0.127483797434826</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.59012666782264</v>
+        <v>-1.65194696673678</v>
       </c>
       <c r="E70" t="n">
-        <v>0.112542877714915</v>
+        <v>0.0992770645365219</v>
       </c>
       <c r="F70" t="n">
-        <v>0.309492913716018</v>
+        <v>0.377330563669873</v>
       </c>
     </row>
     <row r="71">
@@ -1839,16 +1839,16 @@
         <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>0.124656181263922</v>
+        <v>0.103899686123902</v>
       </c>
       <c r="D71" t="n">
-        <v>1.63007580853802</v>
+        <v>1.34634184728479</v>
       </c>
       <c r="E71" t="n">
-        <v>0.103819433855277</v>
+        <v>0.178903222253926</v>
       </c>
       <c r="F71" t="n">
-        <v>0.309492913716018</v>
+        <v>0.393587088958638</v>
       </c>
     </row>
     <row r="72">
@@ -1859,16 +1859,16 @@
         <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.0792580564314036</v>
+        <v>0.129300145174607</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.03642385889422</v>
+        <v>1.67548337057511</v>
       </c>
       <c r="E72" t="n">
-        <v>0.300588282377239</v>
+        <v>0.0945680870997239</v>
       </c>
       <c r="F72" t="n">
-        <v>0.551078517691606</v>
+        <v>0.377330563669873</v>
       </c>
     </row>
     <row r="73">
@@ -1879,16 +1879,16 @@
         <v>12</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.0206997662422272</v>
+        <v>-0.0189102489858781</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.27068202997818</v>
+        <v>-0.245040774443739</v>
       </c>
       <c r="E73" t="n">
-        <v>0.786765779684009</v>
+        <v>0.806542029502812</v>
       </c>
       <c r="F73" t="n">
-        <v>0.916027362498677</v>
+        <v>0.887196232453093</v>
       </c>
     </row>
     <row r="74">
@@ -1899,16 +1899,16 @@
         <v>13</v>
       </c>
       <c r="C74" t="n">
-        <v>0.162774717771661</v>
+        <v>-0.0104899559164335</v>
       </c>
       <c r="D74" t="n">
-        <v>2.12853568102989</v>
+        <v>-0.13592982956296</v>
       </c>
       <c r="E74" t="n">
-        <v>0.033861927042385</v>
+        <v>0.891940513699548</v>
       </c>
       <c r="F74" t="n">
-        <v>0.309492913716018</v>
+        <v>0.891940513699548</v>
       </c>
     </row>
     <row r="75">
@@ -1919,16 +1919,16 @@
         <v>14</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.016158801021707</v>
+        <v>-0.0807295555999448</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.211301761159334</v>
+        <v>-1.046101129577</v>
       </c>
       <c r="E75" t="n">
-        <v>0.83275214772607</v>
+        <v>0.29610339140055</v>
       </c>
       <c r="F75" t="n">
-        <v>0.916027362498677</v>
+        <v>0.537495763198129</v>
       </c>
     </row>
     <row r="76">
@@ -1939,16 +1939,16 @@
         <v>15</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.0540594463270421</v>
+        <v>-0.0510296506770713</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.70691236316714</v>
+        <v>-0.661246984682281</v>
       </c>
       <c r="E76" t="n">
-        <v>0.480004729514559</v>
+        <v>0.508808900092943</v>
       </c>
       <c r="F76" t="n">
-        <v>0.660006503082519</v>
+        <v>0.623107021641293</v>
       </c>
     </row>
     <row r="77">
@@ -1959,16 +1959,16 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0541412747986264</v>
+        <v>0.0509085248848264</v>
       </c>
       <c r="D77" t="n">
-        <v>0.707982399250604</v>
+        <v>0.659677425341261</v>
       </c>
       <c r="E77" t="n">
-        <v>0.47934065424041</v>
+        <v>0.509814835888331</v>
       </c>
       <c r="F77" t="n">
-        <v>0.660006503082519</v>
+        <v>0.623107021641293</v>
       </c>
     </row>
     <row r="78">
@@ -1979,16 +1979,16 @@
         <v>17</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.126425571546606</v>
+        <v>-0.126129705694016</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.65321337192574</v>
+        <v>-1.63440051935347</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0990190003951576</v>
+        <v>0.102908335546329</v>
       </c>
       <c r="F78" t="n">
-        <v>0.309492913716018</v>
+        <v>0.377330563669873</v>
       </c>
     </row>
     <row r="79">
@@ -1999,16 +1999,16 @@
         <v>7</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0855321986046367</v>
+        <v>0.103459905236972</v>
       </c>
       <c r="D79" t="n">
-        <v>0.837425477701765</v>
+        <v>1.01503264438571</v>
       </c>
       <c r="E79" t="n">
-        <v>0.402819725128278</v>
+        <v>0.310662378006296</v>
       </c>
       <c r="F79" t="n">
-        <v>0.65950051515095</v>
+        <v>0.644993750587798</v>
       </c>
     </row>
     <row r="80">
@@ -2019,16 +2019,16 @@
         <v>8</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.00202635914722561</v>
+        <v>-0.0226522511715498</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.0198396019808236</v>
+        <v>-0.222238502493145</v>
       </c>
       <c r="E80" t="n">
-        <v>0.984180550172677</v>
+        <v>0.824233983060949</v>
       </c>
       <c r="F80" t="n">
-        <v>0.984180550172677</v>
+        <v>0.944301968554532</v>
       </c>
     </row>
     <row r="81">
@@ -2039,16 +2039,16 @@
         <v>9</v>
       </c>
       <c r="C81" t="n">
-        <v>0.134033220033281</v>
+        <v>0.00894186951188972</v>
       </c>
       <c r="D81" t="n">
-        <v>1.31228747939834</v>
+        <v>0.0877276026458397</v>
       </c>
       <c r="E81" t="n">
-        <v>0.190124840249583</v>
+        <v>0.930134114993142</v>
       </c>
       <c r="F81" t="n">
-        <v>0.65950051515095</v>
+        <v>0.944301968554532</v>
       </c>
     </row>
     <row r="82">
@@ -2059,16 +2059,16 @@
         <v>10</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.115539926075959</v>
+        <v>-0.107486776946301</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.13122402283882</v>
+        <v>-1.05453979674932</v>
       </c>
       <c r="E82" t="n">
-        <v>0.258592783785286</v>
+        <v>0.292229389917742</v>
       </c>
       <c r="F82" t="n">
-        <v>0.65950051515095</v>
+        <v>0.644993750587798</v>
       </c>
     </row>
     <row r="83">
@@ -2079,16 +2079,16 @@
         <v>11</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0540884180779053</v>
+        <v>-0.00712523764821944</v>
       </c>
       <c r="D83" t="n">
-        <v>0.529566877573134</v>
+        <v>-0.0699048466686998</v>
       </c>
       <c r="E83" t="n">
-        <v>0.596686197717115</v>
+        <v>0.944301968554532</v>
       </c>
       <c r="F83" t="n">
-        <v>0.820443521861032</v>
+        <v>0.944301968554532</v>
       </c>
     </row>
     <row r="84">
@@ -2099,16 +2099,16 @@
         <v>12</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.0954070356090071</v>
+        <v>-0.0950056566868917</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.934107665585612</v>
+        <v>-0.932089032148414</v>
       </c>
       <c r="E84" t="n">
-        <v>0.35077381883406</v>
+        <v>0.35181477304789</v>
       </c>
       <c r="F84" t="n">
-        <v>0.65950051515095</v>
+        <v>0.644993750587798</v>
       </c>
     </row>
     <row r="85">
@@ -2119,16 +2119,16 @@
         <v>13</v>
       </c>
       <c r="C85" t="n">
-        <v>0.00495528215826297</v>
+        <v>0.104528769989481</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0485159927632849</v>
+        <v>1.02551914747832</v>
       </c>
       <c r="E85" t="n">
-        <v>0.961327597329494</v>
+        <v>0.305696191005939</v>
       </c>
       <c r="F85" t="n">
-        <v>0.984180550172677</v>
+        <v>0.644993750587798</v>
       </c>
     </row>
     <row r="86">
@@ -2139,16 +2139,16 @@
         <v>14</v>
       </c>
       <c r="C86" t="n">
-        <v>0.101673020135802</v>
+        <v>0.0582075994252418</v>
       </c>
       <c r="D86" t="n">
-        <v>0.995456434484654</v>
+        <v>0.571067733269423</v>
       </c>
       <c r="E86" t="n">
-        <v>0.320075462248847</v>
+        <v>0.56825275598031</v>
       </c>
       <c r="F86" t="n">
-        <v>0.65950051515095</v>
+        <v>0.781347539472926</v>
       </c>
     </row>
     <row r="87">
@@ -2159,16 +2159,16 @@
         <v>15</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0825012344386349</v>
+        <v>0.0743361871757295</v>
       </c>
       <c r="D87" t="n">
-        <v>0.807750026163993</v>
+        <v>0.729303361236479</v>
       </c>
       <c r="E87" t="n">
-        <v>0.41968214600515</v>
+        <v>0.466214096888846</v>
       </c>
       <c r="F87" t="n">
-        <v>0.65950051515095</v>
+        <v>0.732622152253901</v>
       </c>
     </row>
     <row r="88">
@@ -2179,16 +2179,16 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.0971590800626574</v>
+        <v>-0.0958028418246307</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.951261517438933</v>
+        <v>-0.93991011932775</v>
       </c>
       <c r="E88" t="n">
-        <v>0.342007253225118</v>
+        <v>0.347792576376125</v>
       </c>
       <c r="F88" t="n">
-        <v>0.65950051515095</v>
+        <v>0.644993750587798</v>
       </c>
     </row>
     <row r="89">
@@ -2199,16 +2199,16 @@
         <v>17</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.0140409442823025</v>
+        <v>0.131704736413042</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.137471556499351</v>
+        <v>1.29213927437157</v>
       </c>
       <c r="E89" t="n">
-        <v>0.890722570103284</v>
+        <v>0.19700451886975</v>
       </c>
       <c r="F89" t="n">
-        <v>0.984180550172677</v>
+        <v>0.644993750587798</v>
       </c>
     </row>
     <row r="90">
@@ -2219,16 +2219,16 @@
         <v>7</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.111306484229624</v>
+        <v>-0.12067726910401</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.09445937065408</v>
+        <v>-1.18992956091244</v>
       </c>
       <c r="E90" t="n">
-        <v>0.274367664727275</v>
+        <v>0.234732176589991</v>
       </c>
       <c r="F90" t="n">
-        <v>0.503007385333338</v>
+        <v>0.462043970721153</v>
       </c>
     </row>
     <row r="91">
@@ -2239,16 +2239,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.0330148418637138</v>
+        <v>0.0437036133152689</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.324629811987067</v>
+        <v>0.430936346079421</v>
       </c>
       <c r="E91" t="n">
-        <v>0.745619496610592</v>
+        <v>0.666731095715551</v>
       </c>
       <c r="F91" t="n">
-        <v>0.827741812715881</v>
+        <v>0.735326473915939</v>
       </c>
     </row>
     <row r="92">
@@ -2259,16 +2259,16 @@
         <v>9</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.20769839552278</v>
+        <v>-0.0842587421659985</v>
       </c>
       <c r="D92" t="n">
-        <v>-2.0422660622428</v>
+        <v>-0.830827286804171</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0417360760492035</v>
+        <v>0.406533351975047</v>
       </c>
       <c r="F92" t="n">
-        <v>0.459096836541238</v>
+        <v>0.55898335896569</v>
       </c>
     </row>
     <row r="93">
@@ -2279,16 +2279,16 @@
         <v>10</v>
       </c>
       <c r="C93" t="n">
-        <v>0.173702451536742</v>
+        <v>0.151633934563373</v>
       </c>
       <c r="D93" t="n">
-        <v>1.70798922547745</v>
+        <v>1.49517554145933</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0883617586478161</v>
+        <v>0.135603851364239</v>
       </c>
       <c r="F93" t="n">
-        <v>0.485989672562989</v>
+        <v>0.462043970721153</v>
       </c>
     </row>
     <row r="94">
@@ -2299,16 +2299,16 @@
         <v>11</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.0320920933077857</v>
+        <v>0.135634554342404</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.315556568763342</v>
+        <v>1.33741479975079</v>
       </c>
       <c r="E94" t="n">
-        <v>0.752492557014437</v>
+        <v>0.181795908284388</v>
       </c>
       <c r="F94" t="n">
-        <v>0.827741812715881</v>
+        <v>0.462043970721153</v>
       </c>
     </row>
     <row r="95">
@@ -2319,16 +2319,16 @@
         <v>12</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0190070858416669</v>
+        <v>0.019754745980402</v>
       </c>
       <c r="D95" t="n">
-        <v>0.186893722789084</v>
+        <v>0.194790256565522</v>
       </c>
       <c r="E95" t="n">
-        <v>0.851832312336532</v>
+        <v>0.845649363699252</v>
       </c>
       <c r="F95" t="n">
-        <v>0.851832312336532</v>
+        <v>0.845649363699252</v>
       </c>
     </row>
     <row r="96">
@@ -2339,16 +2339,16 @@
         <v>13</v>
       </c>
       <c r="C96" t="n">
-        <v>0.137290183638979</v>
+        <v>-0.0895981797068938</v>
       </c>
       <c r="D96" t="n">
-        <v>1.34995305100571</v>
+        <v>-0.883476427903651</v>
       </c>
       <c r="E96" t="n">
-        <v>0.177742871318337</v>
+        <v>0.377473731733483</v>
       </c>
       <c r="F96" t="n">
-        <v>0.503007385333338</v>
+        <v>0.55898335896569</v>
       </c>
     </row>
     <row r="97">
@@ -2359,16 +2359,16 @@
         <v>14</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.0929750117275147</v>
+        <v>-0.0434598184882313</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.914208848892642</v>
+        <v>-0.428532424664532</v>
       </c>
       <c r="E97" t="n">
-        <v>0.361120643427405</v>
+        <v>0.668478612650854</v>
       </c>
       <c r="F97" t="n">
-        <v>0.567475296814493</v>
+        <v>0.735326473915939</v>
       </c>
     </row>
     <row r="98">
@@ -2379,16 +2379,16 @@
         <v>15</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.118940705236947</v>
+        <v>-0.119435839902376</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.16952548002712</v>
+        <v>-1.17768853726506</v>
       </c>
       <c r="E98" t="n">
-        <v>0.242841351016825</v>
+        <v>0.239573706301444</v>
       </c>
       <c r="F98" t="n">
-        <v>0.503007385333338</v>
+        <v>0.462043970721153</v>
       </c>
     </row>
     <row r="99">
@@ -2399,16 +2399,16 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>0.118545458382515</v>
+        <v>0.116322793102235</v>
       </c>
       <c r="D99" t="n">
-        <v>1.16563907909955</v>
+        <v>1.14699256245974</v>
       </c>
       <c r="E99" t="n">
-        <v>0.244408064073736</v>
+        <v>0.25202398402972</v>
       </c>
       <c r="F99" t="n">
-        <v>0.503007385333338</v>
+        <v>0.462043970721153</v>
       </c>
     </row>
     <row r="100">
@@ -2419,16 +2419,16 @@
         <v>17</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.0724966534140664</v>
+        <v>-0.205939637517719</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.7128483324152</v>
+        <v>-2.03065303238441</v>
       </c>
       <c r="E100" t="n">
-        <v>0.476327162749557</v>
+        <v>0.0429064644520612</v>
       </c>
       <c r="F100" t="n">
-        <v>0.654949848780641</v>
+        <v>0.462043970721153</v>
       </c>
     </row>
   </sheetData>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0761757033103153</v>
+        <v>0.0697935914744919</v>
       </c>
     </row>
     <row r="3">
@@ -2484,13 +2484,13 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.309492913716018</v>
+        <v>0.377330563669873</v>
       </c>
     </row>
     <row r="4">
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.459096836541238</v>
+        <v>0.462043970721153</v>
       </c>
     </row>
     <row r="5">
@@ -2518,13 +2518,13 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.152453458389753</v>
+        <v>0.615570301973216</v>
       </c>
     </row>
     <row r="6">
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.817821017702153</v>
+        <v>0.787998430293093</v>
       </c>
     </row>
     <row r="7">
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.779798805229336</v>
+        <v>0.856191162558189</v>
       </c>
     </row>
     <row r="8">
@@ -2569,13 +2569,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.224478847415378</v>
+        <v>0.236962350301216</v>
       </c>
     </row>
     <row r="9">
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.65950051515095</v>
+        <v>0.644993750587798</v>
       </c>
     </row>
     <row r="10">
@@ -2609,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.950327173765851</v>
+        <v>0.935525204626051</v>
       </c>
     </row>
   </sheetData>

--- a/04_Features/modules/c_data/module_contrasts.xlsx
+++ b/04_Features/modules/c_data/module_contrasts.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">contrast</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -459,16 +462,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.163440551488145</v>
+        <v>0.106679111156521</v>
       </c>
       <c r="D2" t="n">
-        <v>2.18610964342696</v>
+        <v>1.40793517071191</v>
       </c>
       <c r="E2" t="n">
-        <v>0.029347354796083</v>
+        <v>0.159814159212223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.236962350301216</v>
+        <v>0.351742465640986</v>
       </c>
     </row>
     <row r="3">
@@ -479,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00984263494844101</v>
+        <v>0.0164998065356796</v>
       </c>
       <c r="D3" t="n">
-        <v>0.131650798908855</v>
+        <v>0.217762012447227</v>
       </c>
       <c r="E3" t="n">
-        <v>0.895322222176802</v>
+        <v>0.827709455629325</v>
       </c>
       <c r="F3" t="n">
-        <v>0.895322222176802</v>
+        <v>0.978294435788638</v>
       </c>
     </row>
     <row r="4">
@@ -499,16 +502,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.015351710135656</v>
+        <v>0.00065224547308039</v>
       </c>
       <c r="D4" t="n">
-        <v>0.205337789582088</v>
+        <v>0.0086082395281691</v>
       </c>
       <c r="E4" t="n">
-        <v>0.837405617197178</v>
+        <v>0.993135371570823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.895322222176802</v>
+        <v>0.993135371570823</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +522,16 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.127629100798965</v>
+        <v>0.0840181310144708</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.70711127378182</v>
+        <v>1.10885889796358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0885249459641226</v>
+        <v>0.268060550348461</v>
       </c>
       <c r="F5" t="n">
-        <v>0.265231963101765</v>
+        <v>0.459532372025933</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +542,16 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0100615119654476</v>
+        <v>0.0160367928499266</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1345784025742</v>
+        <v>0.211651226130906</v>
       </c>
       <c r="E6" t="n">
-        <v>0.893008333416084</v>
+        <v>0.832471279931623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.895322222176802</v>
+        <v>0.978294435788638</v>
       </c>
     </row>
     <row r="7">
@@ -559,16 +562,16 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.102025442833883</v>
+        <v>0.00983594256126937</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.36464789443785</v>
+        <v>0.129813318830477</v>
       </c>
       <c r="E7" t="n">
-        <v>0.173079085736162</v>
+        <v>0.896769899472918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.317311657182965</v>
+        <v>0.978294435788638</v>
       </c>
     </row>
     <row r="8">
@@ -579,16 +582,16 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>0.124553760281588</v>
+        <v>-0.102715834816381</v>
       </c>
       <c r="D8" t="n">
-        <v>1.66597685823656</v>
+        <v>-1.3556284342755</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09644798658246</v>
+        <v>0.175871232820493</v>
       </c>
       <c r="F8" t="n">
-        <v>0.265231963101765</v>
+        <v>0.351742465640986</v>
       </c>
     </row>
     <row r="9">
@@ -599,16 +602,16 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0697153223915064</v>
+        <v>0.1052517143198</v>
       </c>
       <c r="D9" t="n">
-        <v>0.932481793453485</v>
+        <v>1.38909659784422</v>
       </c>
       <c r="E9" t="n">
-        <v>0.351612083078058</v>
+        <v>0.165463982982672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.48346661423233</v>
+        <v>0.351742465640986</v>
       </c>
     </row>
     <row r="10">
@@ -619,16 +622,16 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>0.079943899575923</v>
+        <v>-0.118090119538363</v>
       </c>
       <c r="D10" t="n">
-        <v>1.06929478764491</v>
+        <v>-1.55853597587339</v>
       </c>
       <c r="E10" t="n">
-        <v>0.285538134588101</v>
+        <v>0.119782193577689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.448702782924159</v>
+        <v>0.351742465640986</v>
       </c>
     </row>
     <row r="11">
@@ -639,16 +642,16 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.115888431052053</v>
+        <v>0.0703905355048749</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.55007318794376</v>
+        <v>0.929003902902323</v>
       </c>
       <c r="E11" t="n">
-        <v>0.121861319342874</v>
+        <v>0.353365966225374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.268094902554322</v>
+        <v>0.530048949338061</v>
       </c>
     </row>
     <row r="12">
@@ -659,236 +662,236 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>0.151688130833931</v>
+        <v>-0.115775266535295</v>
       </c>
       <c r="D12" t="n">
-        <v>2.02891438256998</v>
+        <v>-1.52798488744835</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0430840636911303</v>
+        <v>0.127191848392785</v>
       </c>
       <c r="F12" t="n">
-        <v>0.236962350301216</v>
+        <v>0.351742465640986</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
       <c r="C13" t="n">
-        <v>0.0599806462511723</v>
+        <v>0.17673132101363</v>
       </c>
       <c r="D13" t="n">
-        <v>0.865771988156715</v>
+        <v>2.33247390162808</v>
       </c>
       <c r="E13" t="n">
-        <v>0.387099121710436</v>
+        <v>0.0200988864856963</v>
       </c>
       <c r="F13" t="n">
-        <v>0.935525204626051</v>
+        <v>0.241186637828355</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0324948861199908</v>
+        <v>0.00620750615759553</v>
       </c>
       <c r="D14" t="n">
-        <v>0.469037329861724</v>
+        <v>0.0882697467928324</v>
       </c>
       <c r="E14" t="n">
-        <v>0.639281220645106</v>
+        <v>0.929700041547618</v>
       </c>
       <c r="F14" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00640984062376629</v>
+        <v>0.00713761272197522</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0925208514320959</v>
+        <v>0.101495713685783</v>
       </c>
       <c r="E15" t="n">
-        <v>0.926327414679895</v>
+        <v>0.91920042888924</v>
       </c>
       <c r="F15" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0201423238526641</v>
+        <v>0.0296371350882687</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.290738110673101</v>
+        <v>0.421435330628778</v>
       </c>
       <c r="E16" t="n">
-        <v>0.771392121562186</v>
+        <v>0.673630717139674</v>
       </c>
       <c r="F16" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.017186749613667</v>
+        <v>-0.036607693468954</v>
       </c>
       <c r="D17" t="n">
-        <v>0.248076793315399</v>
+        <v>-0.520555558244642</v>
       </c>
       <c r="E17" t="n">
-        <v>0.804193690430241</v>
+        <v>0.602922594060989</v>
       </c>
       <c r="F17" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.00701978614699099</v>
+        <v>-0.0168770929595755</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.101324920432923</v>
+        <v>-0.239989568164661</v>
       </c>
       <c r="E18" t="n">
-        <v>0.919339873221008</v>
+        <v>0.810443423226343</v>
       </c>
       <c r="F18" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>0.020024990292107</v>
+        <v>0.00513284709983518</v>
       </c>
       <c r="D19" t="n">
-        <v>0.289044495876493</v>
+        <v>0.0729882665157555</v>
       </c>
       <c r="E19" t="n">
-        <v>0.772686950588943</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="F19" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0115077229662646</v>
+        <v>-0.00682196906601559</v>
       </c>
       <c r="D20" t="n">
-        <v>0.166104648988587</v>
+        <v>-0.097007311277317</v>
       </c>
       <c r="E20" t="n">
-        <v>0.86815284917739</v>
+        <v>0.922762116749113</v>
       </c>
       <c r="F20" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00560771240019357</v>
+        <v>0.0382418583576679</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0809427809996588</v>
+        <v>0.543793122136224</v>
       </c>
       <c r="E21" t="n">
-        <v>0.935525204626051</v>
+        <v>0.586842790792824</v>
       </c>
       <c r="F21" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0200855892274226</v>
+        <v>-0.00735778018481538</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.289919192365902</v>
+        <v>-0.104626459866863</v>
       </c>
       <c r="E22" t="n">
-        <v>0.772018134318984</v>
+        <v>0.916717041909098</v>
       </c>
       <c r="F22" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0199833944208887</v>
+        <v>0.0165351194725005</v>
       </c>
       <c r="D23" t="n">
-        <v>0.288444093207056</v>
+        <v>0.235126759760188</v>
       </c>
       <c r="E23" t="n">
-        <v>0.773146132606368</v>
+        <v>0.814213193755719</v>
       </c>
       <c r="F23" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="24">
@@ -896,19 +899,19 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.122966682906332</v>
+        <v>-0.0185968615643766</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6602897009255</v>
+        <v>-0.264444403235957</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0975868817644897</v>
+        <v>0.79155391705199</v>
       </c>
       <c r="F24" t="n">
-        <v>0.214691139881877</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="25">
@@ -916,199 +919,199 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.136019740501266</v>
+        <v>0.0728360080369906</v>
       </c>
       <c r="D25" t="n">
-        <v>1.83653139971935</v>
+        <v>1.03571640907018</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0669708208120773</v>
+        <v>0.300869324970724</v>
       </c>
       <c r="F25" t="n">
-        <v>0.184169757233212</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.184370431711183</v>
+        <v>-0.0282479596820163</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.48935989562669</v>
+        <v>-0.375738617392864</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0131752591918906</v>
+        <v>0.707281475434882</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0697935914744919</v>
+        <v>0.707281475434882</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>0.076664332400634</v>
+        <v>-0.174783134081328</v>
       </c>
       <c r="D27" t="n">
-        <v>1.03511779373653</v>
+        <v>-2.32486784470737</v>
       </c>
       <c r="E27" t="n">
-        <v>0.301197033966177</v>
+        <v>0.0205059050658457</v>
       </c>
       <c r="F27" t="n">
-        <v>0.473309624803992</v>
+        <v>0.0823720753199149</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>0.174327763077681</v>
+        <v>0.157032962373461</v>
       </c>
       <c r="D28" t="n">
-        <v>2.35376431064444</v>
+        <v>2.08876495263739</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0190346158566796</v>
+        <v>0.0372686188618791</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0697935914744919</v>
+        <v>0.111805856585637</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0609189079196564</v>
+        <v>-0.140563115139643</v>
       </c>
       <c r="D29" t="n">
-        <v>0.822523898507362</v>
+        <v>-1.86969222320957</v>
       </c>
       <c r="E29" t="n">
-        <v>0.411235730263329</v>
+        <v>0.0621507392549162</v>
       </c>
       <c r="F29" t="n">
-        <v>0.502621448099624</v>
+        <v>0.149161774211799</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.00630213084190683</v>
+        <v>-0.0482262037767428</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0850910399744067</v>
+        <v>-0.641478086671017</v>
       </c>
       <c r="E30" t="n">
-        <v>0.932228708918963</v>
+        <v>0.52152614633427</v>
       </c>
       <c r="F30" t="n">
-        <v>0.932228708918963</v>
+        <v>0.625831375601124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0801913374957558</v>
+        <v>0.182486265530603</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.08273923147998</v>
+        <v>2.42733060636971</v>
       </c>
       <c r="E31" t="n">
-        <v>0.279532375115614</v>
+        <v>0.0155867197126552</v>
       </c>
       <c r="F31" t="n">
-        <v>0.473309624803992</v>
+        <v>0.0823720753199149</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.013865770340698</v>
+        <v>0.0616244307168021</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.187214903646668</v>
+        <v>0.819693834733653</v>
       </c>
       <c r="E32" t="n">
-        <v>0.85158064816306</v>
+        <v>0.412807914786857</v>
       </c>
       <c r="F32" t="n">
-        <v>0.932228708918963</v>
+        <v>0.550410553049142</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0634319103425053</v>
+        <v>0.0294183913497299</v>
       </c>
       <c r="D33" t="n">
-        <v>0.85645432537132</v>
+        <v>0.391307047167263</v>
       </c>
       <c r="E33" t="n">
-        <v>0.392224659362268</v>
+        <v>0.695748382816483</v>
       </c>
       <c r="F33" t="n">
-        <v>0.502621448099624</v>
+        <v>0.707281475434882</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.188846736971503</v>
+        <v>0.0933746546791991</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.54979873439385</v>
+        <v>1.24201761980829</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0111252882346163</v>
+        <v>0.214852102760389</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0697935914744919</v>
+        <v>0.429704205520778</v>
       </c>
     </row>
     <row r="35">
@@ -1116,19 +1119,19 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0022894138023219</v>
+        <v>-0.0859094248008704</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.033045831667926</v>
+        <v>-1.14271929226257</v>
       </c>
       <c r="E35" t="n">
-        <v>0.973653408327096</v>
+        <v>0.253739403885517</v>
       </c>
       <c r="F35" t="n">
-        <v>0.973653408327096</v>
+        <v>0.434981835232315</v>
       </c>
     </row>
     <row r="36">
@@ -1136,19 +1139,19 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0923161271859973</v>
+        <v>0.0638551652923891</v>
       </c>
       <c r="D36" t="n">
-        <v>1.33250843343801</v>
+        <v>0.849365822892682</v>
       </c>
       <c r="E36" t="n">
-        <v>0.183400504194503</v>
+        <v>0.396112031180432</v>
       </c>
       <c r="F36" t="n">
-        <v>0.615570301973216</v>
+        <v>0.550410553049142</v>
       </c>
     </row>
     <row r="37">
@@ -1156,179 +1159,179 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.100111689545185</v>
+        <v>-0.174662039385145</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.44503105438895</v>
+        <v>-2.32325711054356</v>
       </c>
       <c r="E37" t="n">
-        <v>0.149179187303412</v>
+        <v>0.0205930188299787</v>
       </c>
       <c r="F37" t="n">
-        <v>0.615570301973216</v>
+        <v>0.0823720753199149</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0749696021627394</v>
+        <v>0.130769293679604</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.08212541165283</v>
+        <v>1.8595184842873</v>
       </c>
       <c r="E38" t="n">
-        <v>0.279804682715098</v>
+        <v>0.0635809801719385</v>
       </c>
       <c r="F38" t="n">
-        <v>0.615570301973216</v>
+        <v>0.527193126890309</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0386932087352775</v>
+        <v>-0.101639507795085</v>
       </c>
       <c r="D39" t="n">
-        <v>0.558505090369032</v>
+        <v>-1.44529757835881</v>
       </c>
       <c r="E39" t="n">
-        <v>0.576790909497371</v>
+        <v>0.149043568699856</v>
       </c>
       <c r="F39" t="n">
-        <v>0.728755774886901</v>
+        <v>0.596174274799422</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0411641619392544</v>
+        <v>0.12027851759581</v>
       </c>
       <c r="D40" t="n">
-        <v>0.594171296082971</v>
+        <v>1.71034132278845</v>
       </c>
       <c r="E40" t="n">
-        <v>0.552710741564234</v>
+        <v>0.0878655211483848</v>
       </c>
       <c r="F40" t="n">
-        <v>0.728755774886901</v>
+        <v>0.527193126890309</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>0.083296048864987</v>
+        <v>0.0405545434450909</v>
       </c>
       <c r="D41" t="n">
-        <v>1.20231091758251</v>
+        <v>0.576679134956139</v>
       </c>
       <c r="E41" t="n">
-        <v>0.229906291317126</v>
+        <v>0.564433489042099</v>
       </c>
       <c r="F41" t="n">
-        <v>0.615570301973216</v>
+        <v>0.752577985389465</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0367315190075245</v>
+        <v>0.0023391557339578</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.530189689954184</v>
+        <v>0.0332624211887106</v>
       </c>
       <c r="E42" t="n">
-        <v>0.596254724907464</v>
+        <v>0.973479501870069</v>
       </c>
       <c r="F42" t="n">
-        <v>0.728755774886901</v>
+        <v>0.973479501870069</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>0.105570069561678</v>
+        <v>0.0525217862080328</v>
       </c>
       <c r="D43" t="n">
-        <v>1.52381834352894</v>
+        <v>0.746851416976462</v>
       </c>
       <c r="E43" t="n">
-        <v>0.128290895611022</v>
+        <v>0.455528287866432</v>
       </c>
       <c r="F43" t="n">
-        <v>0.615570301973216</v>
+        <v>0.752577985389465</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0528908827597301</v>
+        <v>0.04523826678797</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.763437001503801</v>
+        <v>0.643280933331762</v>
       </c>
       <c r="E44" t="n">
-        <v>0.445622448787831</v>
+        <v>0.520356892504631</v>
       </c>
       <c r="F44" t="n">
-        <v>0.728755774886901</v>
+        <v>0.752577985389465</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0170929005462158</v>
+        <v>0.0430142920971172</v>
       </c>
       <c r="D45" t="n">
-        <v>0.246722158132349</v>
+        <v>0.611656368192178</v>
       </c>
       <c r="E45" t="n">
-        <v>0.80524127343169</v>
+        <v>0.541062142586273</v>
       </c>
       <c r="F45" t="n">
-        <v>0.885765400774859</v>
+        <v>0.752577985389465</v>
       </c>
     </row>
     <row r="46">
@@ -1336,19 +1339,19 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0892040134700857</v>
+        <v>-0.0870395789449637</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.1564569324821</v>
+        <v>-1.23768892037679</v>
       </c>
       <c r="E46" t="n">
-        <v>0.248137884170261</v>
+        <v>0.216452007158174</v>
       </c>
       <c r="F46" t="n">
-        <v>0.787998430293093</v>
+        <v>0.649356021474523</v>
       </c>
     </row>
     <row r="47">
@@ -1356,19 +1359,19 @@
         <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0523538404814075</v>
+        <v>-0.030434410883923</v>
       </c>
       <c r="D47" t="n">
-        <v>0.678724638181096</v>
+        <v>-0.432772465191318</v>
       </c>
       <c r="E47" t="n">
-        <v>0.497678323411785</v>
+        <v>0.665379442333905</v>
       </c>
       <c r="F47" t="n">
-        <v>0.787998430293093</v>
+        <v>0.798455330800687</v>
       </c>
     </row>
     <row r="48">
@@ -1376,19 +1379,19 @@
         <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0521669247807174</v>
+        <v>-0.0525746278049512</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.676301429297952</v>
+        <v>-0.747602816050696</v>
       </c>
       <c r="E48" t="n">
-        <v>0.499213728810329</v>
+        <v>0.455075235643833</v>
       </c>
       <c r="F48" t="n">
-        <v>0.787998430293093</v>
+        <v>0.752577985389465</v>
       </c>
     </row>
     <row r="49">
@@ -1396,159 +1399,159 @@
         <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0597525285068298</v>
+        <v>-0.0223069136055875</v>
       </c>
       <c r="D49" t="n">
-        <v>0.77464256524994</v>
+        <v>-0.317200751107671</v>
       </c>
       <c r="E49" t="n">
-        <v>0.438977626701592</v>
+        <v>0.751232738856985</v>
       </c>
       <c r="F49" t="n">
-        <v>0.787998430293093</v>
+        <v>0.81952662420762</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>0.000790828480422799</v>
+        <v>-0.0148843622656003</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0102524431694536</v>
+        <v>-0.192660762575448</v>
       </c>
       <c r="E50" t="n">
-        <v>0.991824643102634</v>
+        <v>0.847308229565406</v>
       </c>
       <c r="F50" t="n">
-        <v>0.991824643102634</v>
+        <v>0.951676696031647</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0563406617206116</v>
+        <v>-0.0518772222493833</v>
       </c>
       <c r="D51" t="n">
-        <v>0.730410508371124</v>
+        <v>-0.671490321218618</v>
       </c>
       <c r="E51" t="n">
-        <v>0.465537979376877</v>
+        <v>0.502239528905025</v>
       </c>
       <c r="F51" t="n">
-        <v>0.787998430293093</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0254205461990204</v>
+        <v>0.0453289188205259</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.329556549484144</v>
+        <v>0.586730147442492</v>
       </c>
       <c r="E52" t="n">
-        <v>0.741895903803947</v>
+        <v>0.557667863955496</v>
       </c>
       <c r="F52" t="n">
-        <v>0.906761660204824</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0954773365369553</v>
+        <v>0.00468438006438979</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.23778542509318</v>
+        <v>0.0606338531200866</v>
       </c>
       <c r="E53" t="n">
-        <v>0.216472628996663</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="F53" t="n">
-        <v>0.787998430293093</v>
+        <v>0.951676696031647</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.00592999795042485</v>
+        <v>0.0506275924890334</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.0768775638292684</v>
+        <v>0.655315316991369</v>
       </c>
       <c r="E54" t="n">
-        <v>0.93875678641436</v>
+        <v>0.512586742383027</v>
       </c>
       <c r="F54" t="n">
-        <v>0.991824643102634</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0303885736072217</v>
+        <v>0.00484475146308899</v>
       </c>
       <c r="D55" t="n">
-        <v>0.393962953562611</v>
+        <v>0.0627096744026743</v>
       </c>
       <c r="E55" t="n">
-        <v>0.693804135936233</v>
+        <v>0.950024466849225</v>
       </c>
       <c r="F55" t="n">
-        <v>0.906761660204824</v>
+        <v>0.951676696031647</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0518948045893386</v>
+        <v>0.0573564263286989</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.672773614017601</v>
+        <v>0.742412247021724</v>
       </c>
       <c r="E56" t="n">
-        <v>0.50145354655015</v>
+        <v>0.458210053214844</v>
       </c>
       <c r="F56" t="n">
-        <v>0.787998430293093</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="57">
@@ -1556,19 +1559,19 @@
         <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0142558917668867</v>
+        <v>-0.0306300639225915</v>
       </c>
       <c r="D57" t="n">
-        <v>0.184729178423445</v>
+        <v>-0.396470562040787</v>
       </c>
       <c r="E57" t="n">
-        <v>0.853528754311322</v>
+        <v>0.691938631269595</v>
       </c>
       <c r="F57" t="n">
-        <v>0.934619895185784</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="58">
@@ -1576,19 +1579,19 @@
         <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0297015893098577</v>
+        <v>0.0591895800604847</v>
       </c>
       <c r="D58" t="n">
-        <v>0.384875971338749</v>
+        <v>0.76614029056042</v>
       </c>
       <c r="E58" t="n">
-        <v>0.700520042093063</v>
+        <v>0.443979077373685</v>
       </c>
       <c r="F58" t="n">
-        <v>0.856191162558189</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="59">
@@ -1596,19 +1599,19 @@
         <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0432250552688277</v>
+        <v>-0.0881528900574695</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.560114307662309</v>
+        <v>-1.14103666107033</v>
       </c>
       <c r="E59" t="n">
-        <v>0.575693828960525</v>
+        <v>0.25443820157249</v>
       </c>
       <c r="F59" t="n">
-        <v>0.856191162558189</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="60">
@@ -1616,19 +1619,19 @@
         <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0477342484394711</v>
+        <v>0.0325143262666986</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.618544854371451</v>
+        <v>0.420860147138891</v>
       </c>
       <c r="E60" t="n">
-        <v>0.536544511799657</v>
+        <v>0.674050403715883</v>
       </c>
       <c r="F60" t="n">
-        <v>0.856191162558189</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="61">
@@ -1636,139 +1639,139 @@
         <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.00633440916779664</v>
+        <v>-0.0954318394594336</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.0820818662556778</v>
+        <v>-1.23525419740184</v>
       </c>
       <c r="E61" t="n">
-        <v>0.934619895185784</v>
+        <v>0.217355661629767</v>
       </c>
       <c r="F61" t="n">
-        <v>0.934619895185784</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0386649949662801</v>
+        <v>0.0855872427333253</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.501024619901937</v>
+        <v>1.10745535193125</v>
       </c>
       <c r="E62" t="n">
-        <v>0.616610765504908</v>
+        <v>0.268665968550084</v>
       </c>
       <c r="F62" t="n">
-        <v>0.856191162558189</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0791082237904604</v>
+        <v>-0.042515028435679</v>
       </c>
       <c r="D63" t="n">
-        <v>1.0250917603972</v>
+        <v>-0.5501228252592</v>
       </c>
       <c r="E63" t="n">
-        <v>0.305897554077598</v>
+        <v>0.582497583848994</v>
       </c>
       <c r="F63" t="n">
-        <v>0.856191162558189</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0372697371117135</v>
+        <v>0.0163440292053376</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.482944738167591</v>
+        <v>0.211483417826287</v>
       </c>
       <c r="E64" t="n">
-        <v>0.629381331979864</v>
+        <v>0.832602132286803</v>
       </c>
       <c r="F64" t="n">
-        <v>0.856191162558189</v>
+        <v>0.912842521828395</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0684061892253046</v>
+        <v>0.125310204547815</v>
       </c>
       <c r="D65" t="n">
-        <v>0.886413795875003</v>
+        <v>1.62145025644156</v>
       </c>
       <c r="E65" t="n">
-        <v>0.375891207982067</v>
+        <v>0.105594594279685</v>
       </c>
       <c r="F65" t="n">
-        <v>0.856191162558189</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.065414268217409</v>
+        <v>0.0835414782985354</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.847644203713804</v>
+        <v>1.08098420156182</v>
       </c>
       <c r="E66" t="n">
-        <v>0.397108801556765</v>
+        <v>0.280260856494352</v>
       </c>
       <c r="F66" t="n">
-        <v>0.856191162558189</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0798099318237034</v>
+        <v>0.00954784692452318</v>
       </c>
       <c r="D67" t="n">
-        <v>1.03418455870079</v>
+        <v>0.123544278776799</v>
       </c>
       <c r="E67" t="n">
-        <v>0.301632515348916</v>
+        <v>0.901729153445781</v>
       </c>
       <c r="F67" t="n">
-        <v>0.856191162558189</v>
+        <v>0.912842521828395</v>
       </c>
     </row>
     <row r="68">
@@ -1776,19 +1779,19 @@
         <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.106421377337123</v>
+        <v>-0.0385374394216661</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.3790181578007</v>
+        <v>-0.498654848249159</v>
       </c>
       <c r="E68" t="n">
-        <v>0.168607688667761</v>
+        <v>0.618256840135387</v>
       </c>
       <c r="F68" t="n">
-        <v>0.393587088958638</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="69">
@@ -1796,19 +1799,19 @@
         <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0734052026251266</v>
+        <v>0.0363797920395403</v>
       </c>
       <c r="D69" t="n">
-        <v>0.951191478911423</v>
+        <v>0.470735989496332</v>
       </c>
       <c r="E69" t="n">
-        <v>0.34204275839881</v>
+        <v>0.638048601066119</v>
       </c>
       <c r="F69" t="n">
-        <v>0.537495763198129</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="70">
@@ -1816,19 +1819,19 @@
         <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.127483797434826</v>
+        <v>-0.0515427592930625</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.65194696673678</v>
+        <v>-0.666937066897473</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0992770645365219</v>
+        <v>0.505141010626103</v>
       </c>
       <c r="F70" t="n">
-        <v>0.377330563669873</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="71">
@@ -1836,19 +1839,19 @@
         <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>0.103899686123902</v>
+        <v>-0.0342974740250952</v>
       </c>
       <c r="D71" t="n">
-        <v>1.34634184728479</v>
+        <v>-0.443791854414128</v>
       </c>
       <c r="E71" t="n">
-        <v>0.178903222253926</v>
+        <v>0.657398187512026</v>
       </c>
       <c r="F71" t="n">
-        <v>0.393587088958638</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="72">
@@ -1856,19 +1859,19 @@
         <v>23</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C72" t="n">
-        <v>0.129300145174607</v>
+        <v>-0.0646640787042194</v>
       </c>
       <c r="D72" t="n">
-        <v>1.67548337057511</v>
+        <v>-0.836720260539568</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0945680870997239</v>
+        <v>0.403176861067897</v>
       </c>
       <c r="F72" t="n">
-        <v>0.377330563669873</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="73">
@@ -1876,119 +1879,119 @@
         <v>23</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.0189102489858781</v>
+        <v>0.00846347351720542</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.245040774443739</v>
+        <v>0.109513038897186</v>
       </c>
       <c r="E73" t="n">
-        <v>0.806542029502812</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="F73" t="n">
-        <v>0.887196232453093</v>
+        <v>0.912842521828395</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.0104899559164335</v>
+        <v>-0.0734300106282945</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.13592982956296</v>
+        <v>-0.950146957252184</v>
       </c>
       <c r="E74" t="n">
-        <v>0.891940513699548</v>
+        <v>0.342527989573741</v>
       </c>
       <c r="F74" t="n">
-        <v>0.891940513699548</v>
+        <v>0.671068819551934</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.0807295555999448</v>
+        <v>-0.115658654721923</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.046101129577</v>
+        <v>-1.49656411491205</v>
       </c>
       <c r="E75" t="n">
-        <v>0.29610339140055</v>
+        <v>0.13518077973217</v>
       </c>
       <c r="F75" t="n">
-        <v>0.537495763198129</v>
+        <v>0.405542339196511</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.0510296506770713</v>
+        <v>0.0530984739829882</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.661246984682281</v>
+        <v>0.687067223033061</v>
       </c>
       <c r="E76" t="n">
-        <v>0.508808900092943</v>
+        <v>0.492380681121931</v>
       </c>
       <c r="F76" t="n">
-        <v>0.623107021641293</v>
+        <v>0.671068819551934</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0509085248848264</v>
+        <v>-0.055807454036919</v>
       </c>
       <c r="D77" t="n">
-        <v>0.659677425341261</v>
+        <v>-0.72212004589766</v>
       </c>
       <c r="E77" t="n">
-        <v>0.509814835888331</v>
+        <v>0.470581328112939</v>
       </c>
       <c r="F77" t="n">
-        <v>0.623107021641293</v>
+        <v>0.671068819551934</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.126129705694016</v>
+        <v>0.0329761187878349</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.63440051935347</v>
+        <v>0.426694190293018</v>
       </c>
       <c r="E78" t="n">
-        <v>0.102908335546329</v>
+        <v>0.669798293359957</v>
       </c>
       <c r="F78" t="n">
-        <v>0.377330563669873</v>
+        <v>0.774525374998041</v>
       </c>
     </row>
     <row r="79">
@@ -1996,19 +1999,19 @@
         <v>24</v>
       </c>
       <c r="B79" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C79" t="n">
-        <v>0.103459905236972</v>
+        <v>0.139512326247094</v>
       </c>
       <c r="D79" t="n">
-        <v>1.01503264438571</v>
+        <v>1.80521848149879</v>
       </c>
       <c r="E79" t="n">
-        <v>0.310662378006296</v>
+        <v>0.0716830412962833</v>
       </c>
       <c r="F79" t="n">
-        <v>0.644993750587798</v>
+        <v>0.384311055119259</v>
       </c>
     </row>
     <row r="80">
@@ -2016,19 +2019,19 @@
         <v>24</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.0226522511715498</v>
+        <v>-0.022151275492834</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.222238502493145</v>
+        <v>-0.286626228549954</v>
       </c>
       <c r="E80" t="n">
-        <v>0.824233983060949</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="F80" t="n">
-        <v>0.944301968554532</v>
+        <v>0.774525374998041</v>
       </c>
     </row>
     <row r="81">
@@ -2036,19 +2039,19 @@
         <v>24</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C81" t="n">
-        <v>0.00894186951188972</v>
+        <v>0.022783891292153</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0877276026458397</v>
+        <v>0.294811954953771</v>
       </c>
       <c r="E81" t="n">
-        <v>0.930134114993142</v>
+        <v>0.76826826393477</v>
       </c>
       <c r="F81" t="n">
-        <v>0.944301968554532</v>
+        <v>0.774525374998041</v>
       </c>
     </row>
     <row r="82">
@@ -2056,19 +2059,19 @@
         <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.107486776946301</v>
+        <v>0.1288714743311</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.05453979674932</v>
+        <v>1.66753127453744</v>
       </c>
       <c r="E82" t="n">
-        <v>0.292229389917742</v>
+        <v>0.0960777637798146</v>
       </c>
       <c r="F82" t="n">
-        <v>0.644993750587798</v>
+        <v>0.384311055119259</v>
       </c>
     </row>
     <row r="83">
@@ -2076,19 +2079,19 @@
         <v>24</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.00712523764821944</v>
+        <v>-0.0897724879420425</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.0699048466686998</v>
+        <v>-1.16161029439131</v>
       </c>
       <c r="E83" t="n">
-        <v>0.944301968554532</v>
+        <v>0.245985886443367</v>
       </c>
       <c r="F83" t="n">
-        <v>0.944301968554532</v>
+        <v>0.590366127464082</v>
       </c>
     </row>
     <row r="84">
@@ -2096,19 +2099,19 @@
         <v>24</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.0950056566868917</v>
+        <v>0.0517657143931209</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.932089032148414</v>
+        <v>0.669821992394716</v>
       </c>
       <c r="E84" t="n">
-        <v>0.35181477304789</v>
+        <v>0.503301614663951</v>
       </c>
       <c r="F84" t="n">
-        <v>0.644993750587798</v>
+        <v>0.671068819551934</v>
       </c>
     </row>
     <row r="85">
@@ -2116,99 +2119,99 @@
         <v>24</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C85" t="n">
-        <v>0.104528769989481</v>
+        <v>-0.143891652262352</v>
       </c>
       <c r="D85" t="n">
-        <v>1.02551914747832</v>
+        <v>-1.86188473079673</v>
       </c>
       <c r="E85" t="n">
-        <v>0.305696191005939</v>
+        <v>0.063245917851087</v>
       </c>
       <c r="F85" t="n">
-        <v>0.644993750587798</v>
+        <v>0.384311055119259</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0582075994252418</v>
+        <v>0.100471604998926</v>
       </c>
       <c r="D86" t="n">
-        <v>0.571067733269423</v>
+        <v>0.971905243659507</v>
       </c>
       <c r="E86" t="n">
-        <v>0.56825275598031</v>
+        <v>0.331599736894066</v>
       </c>
       <c r="F86" t="n">
-        <v>0.781347539472926</v>
+        <v>0.708162829885467</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0743361871757295</v>
+        <v>0.00936219381370434</v>
       </c>
       <c r="D87" t="n">
-        <v>0.729303361236479</v>
+        <v>0.0905645456723136</v>
       </c>
       <c r="E87" t="n">
-        <v>0.466214096888846</v>
+        <v>0.927877351922577</v>
       </c>
       <c r="F87" t="n">
-        <v>0.732622152253901</v>
+        <v>0.96373210668647</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.0958028418246307</v>
+        <v>-0.0289848896151883</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.93991011932775</v>
+        <v>-0.280383360096564</v>
       </c>
       <c r="E88" t="n">
-        <v>0.347792576376125</v>
+        <v>0.779307298309783</v>
       </c>
       <c r="F88" t="n">
-        <v>0.644993750587798</v>
+        <v>0.93516875797174</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C89" t="n">
-        <v>0.131704736413042</v>
+        <v>0.120625824483425</v>
       </c>
       <c r="D89" t="n">
-        <v>1.29213927437157</v>
+        <v>1.16686571631304</v>
       </c>
       <c r="E89" t="n">
-        <v>0.19700451886975</v>
+        <v>0.243858820361034</v>
       </c>
       <c r="F89" t="n">
-        <v>0.644993750587798</v>
+        <v>0.708162829885467</v>
       </c>
     </row>
     <row r="90">
@@ -2216,19 +2219,19 @@
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.12067726910401</v>
+        <v>0.0329138858095021</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.18992956091244</v>
+        <v>0.318390237797111</v>
       </c>
       <c r="E90" t="n">
-        <v>0.234732176589991</v>
+        <v>0.750330975512539</v>
       </c>
       <c r="F90" t="n">
-        <v>0.462043970721153</v>
+        <v>0.93516875797174</v>
       </c>
     </row>
     <row r="91">
@@ -2236,19 +2239,19 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0437036133152689</v>
+        <v>0.00470309546143418</v>
       </c>
       <c r="D91" t="n">
-        <v>0.430936346079421</v>
+        <v>0.0454950743590489</v>
       </c>
       <c r="E91" t="n">
-        <v>0.666731095715551</v>
+        <v>0.96373210668647</v>
       </c>
       <c r="F91" t="n">
-        <v>0.735326473915939</v>
+        <v>0.96373210668647</v>
       </c>
     </row>
     <row r="92">
@@ -2256,19 +2259,19 @@
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.0842587421659985</v>
+        <v>-0.095893865750365</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.830827286804171</v>
+        <v>-0.927622794107422</v>
       </c>
       <c r="E92" t="n">
-        <v>0.406533351975047</v>
+        <v>0.354081414942733</v>
       </c>
       <c r="F92" t="n">
-        <v>0.55898335896569</v>
+        <v>0.708162829885467</v>
       </c>
     </row>
     <row r="93">
@@ -2276,19 +2279,19 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C93" t="n">
-        <v>0.151633934563373</v>
+        <v>0.0670098559621318</v>
       </c>
       <c r="D93" t="n">
-        <v>1.49517554145933</v>
+        <v>0.648215288161871</v>
       </c>
       <c r="E93" t="n">
-        <v>0.135603851364239</v>
+        <v>0.517163614377893</v>
       </c>
       <c r="F93" t="n">
-        <v>0.462043970721153</v>
+        <v>0.886566196076388</v>
       </c>
     </row>
     <row r="94">
@@ -2296,19 +2299,19 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>0.135634554342404</v>
+        <v>-0.110732339353547</v>
       </c>
       <c r="D94" t="n">
-        <v>1.33741479975079</v>
+        <v>-1.0711617601963</v>
       </c>
       <c r="E94" t="n">
-        <v>0.181795908284388</v>
+        <v>0.284648787287383</v>
       </c>
       <c r="F94" t="n">
-        <v>0.462043970721153</v>
+        <v>0.708162829885467</v>
       </c>
     </row>
     <row r="95">
@@ -2316,19 +2319,19 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>0.019754745980402</v>
+        <v>0.0538554160323744</v>
       </c>
       <c r="D95" t="n">
-        <v>0.194790256565522</v>
+        <v>0.520966707378554</v>
       </c>
       <c r="E95" t="n">
-        <v>0.845649363699252</v>
+        <v>0.602636367404753</v>
       </c>
       <c r="F95" t="n">
-        <v>0.845649363699252</v>
+        <v>0.903954551107129</v>
       </c>
     </row>
     <row r="96">
@@ -2336,19 +2339,19 @@
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.0895981797068938</v>
+        <v>-0.097178404970918</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.883476427903651</v>
+        <v>-0.940048696969779</v>
       </c>
       <c r="E96" t="n">
-        <v>0.377473731733483</v>
+        <v>0.347677514706437</v>
       </c>
       <c r="F96" t="n">
-        <v>0.55898335896569</v>
+        <v>0.708162829885467</v>
       </c>
     </row>
     <row r="97">
@@ -2356,79 +2359,259 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.0434598184882313</v>
+        <v>0.103895312976639</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.428532424664532</v>
+        <v>1.00502425013237</v>
       </c>
       <c r="E97" t="n">
-        <v>0.668478612650854</v>
+        <v>0.315404517029433</v>
       </c>
       <c r="F97" t="n">
-        <v>0.735326473915939</v>
+        <v>0.708162829885467</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.119435839902376</v>
+        <v>-0.15901725336162</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.17768853726506</v>
+        <v>-1.54469364575475</v>
       </c>
       <c r="E98" t="n">
-        <v>0.239573706301444</v>
+        <v>0.123096282731459</v>
       </c>
       <c r="F98" t="n">
-        <v>0.462043970721153</v>
+        <v>0.418656058555944</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>0.116322793102235</v>
+        <v>-0.0731436262862439</v>
       </c>
       <c r="D99" t="n">
-        <v>1.14699256245974</v>
+        <v>-0.7105172071793</v>
       </c>
       <c r="E99" t="n">
-        <v>0.25202398402972</v>
+        <v>0.477737376897154</v>
       </c>
       <c r="F99" t="n">
-        <v>0.462043970721153</v>
+        <v>0.818978360395121</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B100" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.0367544447776506</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.357032687340982</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.721228266060265</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.865473919272318</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>26</v>
+      </c>
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.181117658584734</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-1.7593769885686</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.0791668720684252</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.418656058555944</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.0505653595107006</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-0.491191917105115</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.623520974891628</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.831361299855504</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>26</v>
+      </c>
+      <c r="B103" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.12996447932257</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1.26247499022552</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.207406635967208</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.4977759263213</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>26</v>
+      </c>
+      <c r="B104" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.0163861639288321</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.159175201206637</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.873599509560133</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.894985223087413</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>26</v>
+      </c>
+      <c r="B105" t="s">
+        <v>14</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.0135959007473873</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.132070583844396</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.894985223087413</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.894985223087413</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>26</v>
+      </c>
+      <c r="B106" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.180414233624163</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.75254391829548</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.0803351456903422</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.418656058555944</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>26</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.0554750139169474</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.53888430144617</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.590222928822899</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.831361299855504</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>26</v>
+      </c>
+      <c r="B108" t="s">
         <v>17</v>
       </c>
-      <c r="C100" t="n">
-        <v>-0.205939637517719</v>
-      </c>
-      <c r="D100" t="n">
-        <v>-2.03065303238441</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0.0429064644520612</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.462043970721153</v>
+      <c r="C108" t="n">
+        <v>0.11642979309734</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1.1309990442673</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.258634732869426</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.517269465738852</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>26</v>
+      </c>
+      <c r="B109" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.152355125779557</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-1.47997773647026</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.139552019518648</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.418656058555944</v>
       </c>
     </row>
   </sheetData>
@@ -2447,41 +2630,41 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0697935914744919</v>
+        <v>0.0823720753199149</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -2490,32 +2673,32 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.377330563669873</v>
+        <v>0.384311055119259</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.462043970721153</v>
+        <v>0.418656058555944</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2524,15 +2707,15 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.615570301973216</v>
+        <v>0.527193126890309</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2541,15 +2724,15 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.787998430293093</v>
+        <v>0.922584841692793</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -2558,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.856191162558189</v>
+        <v>0.876530916682701</v>
       </c>
     </row>
     <row r="8">
@@ -2566,24 +2749,24 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.236962350301216</v>
+        <v>0.241186637828355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -2592,15 +2775,15 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.644993750587798</v>
+        <v>0.708162829885467</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -2609,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.935525204626051</v>
+        <v>0.941846637807116</v>
       </c>
     </row>
   </sheetData>
